--- a/LuBan/MiniTemplate/Datas/__enums__.xlsx
+++ b/LuBan/MiniTemplate/Datas/__enums__.xlsx
@@ -1,20 +1,309 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12900"/>
+    <workbookView xWindow="120" yWindow="90" windowWidth="14940" windowHeight="6165" firstSheet="3" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Overview" sheetId="13" state="hidden" r:id="rId1"/>
+    <sheet name="Base Spin Sequence" sheetId="14" state="hidden" r:id="rId2"/>
+    <sheet name="추가 이미지" sheetId="15" state="hidden" r:id="rId3"/>
+    <sheet name="Sheet1 (2)" sheetId="117" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames>
+    <definedName name="WebWps_Link_1" hidden="1">#REF!</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="130">
+  <si>
+    <t>Jungle Quest</t>
+  </si>
+  <si>
+    <t>Reel</t>
+  </si>
+  <si>
+    <t>3x5</t>
+  </si>
+  <si>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>243ways</t>
+  </si>
+  <si>
+    <t>Base Rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243 way 게임입니다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">와일드 심볼은 2,3,4 릴에서만 출력됩니다. </t>
+  </si>
+  <si>
+    <t>Free Spins Rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scatter 심볼이 1번 릴 부터 차례대로 3개 이상출력되면 프리스핀에 진입합니다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">프리스핀에 진입하면 6개의 선택지가 제공됩니다. 각 선택지에 따라 프리스핀 개수와 멀티플라이어가 변경됩니다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">와일드 심볼이 출력되고, 와일드를 포함하여 윈이 발생하면 멀티플라이어와 추가 프리스핀이 제공됩니다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">프리스핀 중 Scatter 심볼이 1번 릴 부터 차례대로 3개 이상 출력되면, 최초 프리스핀과 동일한 프리스핀 개수를 획득합니다. </t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Client name</t>
+  </si>
+  <si>
+    <t>WW</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>FF</t>
+  </si>
+  <si>
+    <t>GG</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>JJ</t>
+  </si>
+  <si>
+    <t>KK</t>
+  </si>
+  <si>
+    <t>LL</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Wild</t>
+  </si>
+  <si>
+    <t>Tiger</t>
+  </si>
+  <si>
+    <t>Elephant</t>
+  </si>
+  <si>
+    <t>Monkey</t>
+  </si>
+  <si>
+    <t>Snake</t>
+  </si>
+  <si>
+    <t>Flower</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Scatter</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Eval Type</t>
+  </si>
+  <si>
+    <t>Pay 5</t>
+  </si>
+  <si>
+    <t>Pay 4</t>
+  </si>
+  <si>
+    <t>Pay 3</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>Way</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>Royal A</t>
+  </si>
+  <si>
+    <t>Royal K</t>
+  </si>
+  <si>
+    <t>Royal Q</t>
+  </si>
+  <si>
+    <t>Royal J</t>
+  </si>
+  <si>
+    <t>Royal 10</t>
+  </si>
+  <si>
+    <t>Royal 9</t>
+  </si>
+  <si>
+    <t>Base Game</t>
+  </si>
+  <si>
+    <t>Free Spins Reel Strips</t>
+  </si>
+  <si>
+    <t>Stop Index</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">프리스핀 선택지 </t>
+  </si>
+  <si>
+    <t>Initial Free Spins</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Additional Games</t>
+  </si>
+  <si>
+    <t>랜덤 와일드 선택지</t>
+  </si>
+  <si>
+    <t>Initial Games</t>
+  </si>
+  <si>
+    <t>Multiplier Set</t>
+  </si>
+  <si>
+    <t>2 3 5</t>
+  </si>
+  <si>
+    <t>3 5 8</t>
+  </si>
+  <si>
+    <t>5 8 10</t>
+  </si>
+  <si>
+    <t>10 15 30</t>
+  </si>
+  <si>
+    <t>15 30 40</t>
+  </si>
+  <si>
+    <t>Free Spins</t>
+  </si>
+  <si>
+    <t>디자인 셋팅 사항</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 스캐터 심볼은 스탑 이펙트가 필요합니다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. 익스펙테이션 이펙트가 필요합니다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. 윈보더 애니가 필요합니다. </t>
+  </si>
+  <si>
+    <t>팝업</t>
+  </si>
+  <si>
+    <t>1. 프리스핀 팝업</t>
+  </si>
+  <si>
+    <t>2. 추가 프리스핀 팝업</t>
+  </si>
+  <si>
+    <t>3. 결과 팝업</t>
+  </si>
+  <si>
+    <t>- 붉은색 영역 Coins 삭제</t>
+  </si>
   <si>
     <t>##var</t>
   </si>
@@ -139,33 +428,114 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="NanumGothic"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="NanumGothic"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="NanumGothic"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -173,14 +543,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -188,7 +558,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -196,7 +566,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -204,7 +574,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -212,7 +582,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -220,14 +590,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -235,7 +605,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -243,7 +613,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -251,14 +621,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -266,47 +636,68 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,6 +707,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,10 +1055,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="53">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -647,202 +1072,281 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="30">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="50" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="53">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="표준 2" xfId="49"/>
+    <cellStyle name="Normal 10" xfId="50"/>
+    <cellStyle name="Normal 5 2 2" xfId="51"/>
+    <cellStyle name="표준 8" xfId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -851,10 +1355,4333 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>54373</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>75</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1102123</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>61035</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1857375" y="3629025"/>
+          <a:ext cx="1047750" cy="1156335"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>9044</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>198094</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>8409</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38074</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 14"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5203190" y="3607435"/>
+          <a:ext cx="1129665" cy="1154430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>7388</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>198094</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6753</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38074</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 15"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4070985" y="3607435"/>
+          <a:ext cx="1129665" cy="1154430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>137839</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85246</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1019854</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>96676</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 16"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10983595" y="3714115"/>
+          <a:ext cx="882015" cy="887730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>139495</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85246</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1022145</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>96676</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 17"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12115165" y="3714115"/>
+          <a:ext cx="882650" cy="887730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>10700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>198094</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>10700</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38074</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 18"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6334760" y="3607435"/>
+          <a:ext cx="1130300" cy="1154430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>12356</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>198094</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>11721</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38074</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 19"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7466965" y="3607435"/>
+          <a:ext cx="1129665" cy="1154430"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>136183</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85246</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1018198</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>96676</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 22"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9851390" y="3714115"/>
+          <a:ext cx="882015" cy="887730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>134527</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85246</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1017177</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>96676</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 23"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8719185" y="3714115"/>
+          <a:ext cx="882650" cy="887730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1002596</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>37194</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>145346</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>364</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 15"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2805430" y="3665855"/>
+          <a:ext cx="1403350" cy="1058545"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>141151</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85246</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1023166</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>96676</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 17"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13247370" y="3714115"/>
+          <a:ext cx="882015" cy="887730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>142808</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85246</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1025458</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>96676</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 17"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14378940" y="3714115"/>
+          <a:ext cx="882650" cy="887730"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>30165</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>21780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1067120</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>177355</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 17"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15396845" y="3650615"/>
+          <a:ext cx="1036955" cy="1031875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rounded Rectangle 62"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="793750" y="2676525"/>
+          <a:ext cx="2914650" cy="2178050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 8236"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0"/>
+            <a:t>Free</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" baseline="0"/>
+            <a:t> Spins</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rounded Rectangle 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082675" y="612775"/>
+          <a:ext cx="2336800" cy="406400"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Spin</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>29633</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>105833</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rounded Rectangle 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082675" y="1143635"/>
+          <a:ext cx="2336800" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Stop</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rounded Rectangle 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082675" y="1654175"/>
+          <a:ext cx="2336800" cy="444500"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Community</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rounded Rectangle 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082675" y="4911725"/>
+          <a:ext cx="2336800" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Total Win</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rounded Rectangle 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082675" y="5489575"/>
+          <a:ext cx="2336800" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Symbol Win</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rounded Rectangle 30"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082675" y="3114675"/>
+          <a:ext cx="2336800" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Free Spins Popup</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rounded Rectangle 32"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082675" y="3629025"/>
+          <a:ext cx="2336800" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1400" b="1"/>
+            <a:t>프리스핀 진행</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Rounded Rectangle 36"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082675" y="4143375"/>
+          <a:ext cx="2336800" cy="552450"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Free</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0"/>
+            <a:t> spins</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400" b="1" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Result</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0"/>
+            <a:t> Popup</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rounded Rectangle 42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082675" y="6054725"/>
+          <a:ext cx="2336800" cy="374650"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Big</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0"/>
+            <a:t> Win</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>339725</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Rounded Rectangle 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="625475"/>
+          <a:ext cx="2336800" cy="406400"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Spin</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>75045</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>339725</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>151245</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Rounded Rectangle 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="1189355"/>
+          <a:ext cx="2336800" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Stop</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>42715</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>339725</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>118915</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Rounded Rectangle 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="4071620"/>
+          <a:ext cx="2336800" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Total Win</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>105060</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>339725</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>181260</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Rounded Rectangle 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="4648200"/>
+          <a:ext cx="2336800" cy="409575"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Symbol</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Win</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>339725</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="Rounded Rectangle 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="5197475"/>
+          <a:ext cx="2336800" cy="374650"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Big Win</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358775</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rounded Rectangle 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1082675" y="2168525"/>
+          <a:ext cx="2336800" cy="444500"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Scatter Symbol ani</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>123535</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>339725</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>9235</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rounded Rectangle 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="1751965"/>
+          <a:ext cx="2336800" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Scatter Symbol ani</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>211280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>339725</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>96980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rounded Rectangle 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="2314575"/>
+          <a:ext cx="2336800" cy="439420"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Add Free Spin</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0"/>
+            <a:t> Popup</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>83125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>339725</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>184725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Rounded Rectangle 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="2911475"/>
+          <a:ext cx="2336800" cy="431800"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Multiplier ani</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>170870</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>339725</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>56570</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Rounded Rectangle 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5991225" y="3514090"/>
+          <a:ext cx="2336800" cy="400050"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Add</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1"/>
+            <a:t>Free Spin ani</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="en-US" sz="1400" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>228601</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2988510" cy="398163"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 18"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22021800" y="4470400"/>
+          <a:ext cx="2988310" cy="398145"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>10 FREE</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2400" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> SPINS PLAYED</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2400">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>12750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>67995</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7569200" y="2070100"/>
+          <a:ext cx="5638800" cy="2969895"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>584835</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="850900" y="2120900"/>
+          <a:ext cx="5601335" cy="2946400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>431800</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>67945</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 11"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13843000" y="2070100"/>
+          <a:ext cx="5651500" cy="2969895"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>203200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="직사각형 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16129000" y="3702050"/>
+          <a:ext cx="1054100" cy="241300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle>
+          <a:defPPr>
+            <a:defRPr lang="zh-CN">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:defPPr>
+          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Ofis Teması">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Ofis">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -862,44 +5689,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Ofis">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -932,9 +5759,9 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -964,7 +5791,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Ofis">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -973,131 +5800,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1109,221 +5965,2695 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A2:Y104"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="8.83333333333333" style="5"/>
+    <col min="2" max="16" width="14.8333333333333" style="5" customWidth="1"/>
+    <col min="17" max="16384" width="8.83333333333333" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="31.5" customHeight="1" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="3" spans="14:14">
+      <c r="N3" s="26"/>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" s="8" customFormat="1" ht="17.25" spans="2:15">
+      <c r="B17" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="11">
+        <v>0</v>
+      </c>
+      <c r="D17" s="11">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11">
+        <v>2</v>
+      </c>
+      <c r="F17" s="11">
+        <v>3</v>
+      </c>
+      <c r="G17" s="11">
+        <v>4</v>
+      </c>
+      <c r="H17" s="11">
+        <v>5</v>
+      </c>
+      <c r="I17" s="11">
+        <v>6</v>
+      </c>
+      <c r="J17" s="11">
+        <v>7</v>
+      </c>
+      <c r="K17" s="11">
+        <v>8</v>
+      </c>
+      <c r="L17" s="11">
+        <v>9</v>
+      </c>
+      <c r="M17" s="11">
+        <v>10</v>
+      </c>
+      <c r="N17" s="11">
+        <v>10</v>
+      </c>
+      <c r="O17" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" s="8" customFormat="1" ht="17.25" spans="2:15">
+      <c r="B18" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" s="8" customFormat="1" ht="17.25" spans="2:15">
+      <c r="B19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="M19" s="14">
+        <v>10</v>
+      </c>
+      <c r="N19" s="14">
+        <v>9</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" s="8" customFormat="1" ht="17.25" spans="2:15">
+      <c r="B20" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+    </row>
+    <row r="21" s="8" customFormat="1" ht="17.25" spans="2:15">
+      <c r="B21" s="10"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+    </row>
+    <row r="22" s="8" customFormat="1" ht="17.25" spans="2:15">
+      <c r="B22" s="10"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+    </row>
+    <row r="23" s="8" customFormat="1" ht="17.25" spans="2:15">
+      <c r="B23" s="10"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+    </row>
+    <row r="24" s="8" customFormat="1" ht="17.25" spans="2:15">
+      <c r="B24" s="10"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+    </row>
+    <row r="25" ht="17" customHeight="1"/>
+    <row r="26" ht="17" customHeight="1"/>
+    <row r="27" ht="17" customHeight="1"/>
+    <row r="28" ht="17" customHeight="1" spans="2:7">
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17"/>
+    </row>
+    <row r="29" ht="17" customHeight="1" spans="2:23">
+      <c r="B29" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="W29" s="27"/>
+    </row>
+    <row r="30" ht="17" customHeight="1" spans="2:23">
+      <c r="B30" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="W30" s="27"/>
+    </row>
+    <row r="31" ht="17" customHeight="1" spans="2:23">
+      <c r="B31" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="20">
+        <v>1000</v>
+      </c>
+      <c r="F31" s="19">
+        <v>100</v>
+      </c>
+      <c r="G31" s="19">
+        <v>50</v>
+      </c>
+      <c r="W31" s="27"/>
+    </row>
+    <row r="32" ht="17" customHeight="1" spans="2:23">
+      <c r="B32" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="19">
+        <v>800</v>
+      </c>
+      <c r="F32" s="19">
+        <v>100</v>
+      </c>
+      <c r="G32" s="19">
+        <v>35</v>
+      </c>
+      <c r="W32" s="27"/>
+    </row>
+    <row r="33" spans="2:23">
+      <c r="B33" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="19">
+        <v>800</v>
+      </c>
+      <c r="F33" s="19">
+        <v>100</v>
+      </c>
+      <c r="G33" s="19">
+        <v>30</v>
+      </c>
+      <c r="W33" s="27"/>
+    </row>
+    <row r="34" spans="2:23">
+      <c r="B34" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="19">
+        <v>300</v>
+      </c>
+      <c r="F34" s="19">
+        <v>50</v>
+      </c>
+      <c r="G34" s="19">
+        <v>20</v>
+      </c>
+      <c r="W34" s="27"/>
+    </row>
+    <row r="35" spans="2:23">
+      <c r="B35" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" s="19">
+        <v>300</v>
+      </c>
+      <c r="F35" s="19">
+        <v>35</v>
+      </c>
+      <c r="G35" s="19">
+        <v>15</v>
+      </c>
+      <c r="W35" s="27"/>
+    </row>
+    <row r="36" spans="2:23">
+      <c r="B36" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="19">
+        <v>200</v>
+      </c>
+      <c r="F36" s="19">
+        <v>30</v>
+      </c>
+      <c r="G36" s="19">
+        <v>10</v>
+      </c>
+      <c r="W36" s="27"/>
+    </row>
+    <row r="37" spans="2:23">
+      <c r="B37" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="19">
+        <v>200</v>
+      </c>
+      <c r="F37" s="19">
+        <v>20</v>
+      </c>
+      <c r="G37" s="19">
+        <v>10</v>
+      </c>
+      <c r="W37" s="27"/>
+    </row>
+    <row r="38" spans="2:23">
+      <c r="B38" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" s="19">
+        <v>100</v>
+      </c>
+      <c r="F38" s="19">
+        <v>15</v>
+      </c>
+      <c r="G38" s="19">
+        <v>10</v>
+      </c>
+      <c r="W38" s="27"/>
+    </row>
+    <row r="39" spans="2:23">
+      <c r="B39" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="19">
+        <v>100</v>
+      </c>
+      <c r="F39" s="19">
+        <v>15</v>
+      </c>
+      <c r="G39" s="19">
+        <v>10</v>
+      </c>
+      <c r="W39" s="27"/>
+    </row>
+    <row r="40" spans="2:23">
+      <c r="B40" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="19">
+        <v>100</v>
+      </c>
+      <c r="F40" s="19">
+        <v>15</v>
+      </c>
+      <c r="G40" s="19">
+        <v>5</v>
+      </c>
+      <c r="W40" s="27"/>
+    </row>
+    <row r="41" spans="2:23">
+      <c r="B41" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="19">
+        <v>100</v>
+      </c>
+      <c r="F41" s="19">
+        <v>10</v>
+      </c>
+      <c r="G41" s="19">
+        <v>5</v>
+      </c>
+      <c r="W41" s="27"/>
+    </row>
+    <row r="42" spans="2:23">
+      <c r="B42" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" s="19">
+        <v>50</v>
+      </c>
+      <c r="F42" s="21">
+        <v>10</v>
+      </c>
+      <c r="G42" s="21">
+        <v>5</v>
+      </c>
+      <c r="W42" s="27"/>
+    </row>
+    <row r="43" spans="23:23">
+      <c r="W43" s="27"/>
+    </row>
+    <row r="44" spans="2:23">
+      <c r="B44" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="I44" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
+      <c r="W44" s="27"/>
+    </row>
+    <row r="45" spans="2:23">
+      <c r="B45" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="I45" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="J45" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K45" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="L45" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="M45" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="N45" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="W45" s="27"/>
+    </row>
+    <row r="46" spans="2:23">
+      <c r="B46" s="23">
+        <v>0</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="23">
+        <v>0</v>
+      </c>
+      <c r="J46" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="M46" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="N46" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="W46" s="27"/>
+    </row>
+    <row r="47" spans="2:23">
+      <c r="B47" s="23">
+        <v>1</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G47" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="23">
+        <v>1</v>
+      </c>
+      <c r="J47" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K47" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="L47" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="N47" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="W47" s="27"/>
+    </row>
+    <row r="48" spans="2:23">
+      <c r="B48" s="23">
+        <v>2</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" s="23">
+        <v>2</v>
+      </c>
+      <c r="J48" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="N48" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="W48" s="27"/>
+    </row>
+    <row r="49" spans="2:23">
+      <c r="B49" s="23">
+        <v>3</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="23">
+        <v>3</v>
+      </c>
+      <c r="J49" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K49" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="L49" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="M49" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="N49" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="W49" s="27"/>
+    </row>
+    <row r="50" spans="2:23">
+      <c r="B50" s="23">
+        <v>4</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I50" s="23">
+        <v>4</v>
+      </c>
+      <c r="J50" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K50" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="L50" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M50" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="N50" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="W50" s="27"/>
+    </row>
+    <row r="51" spans="2:23">
+      <c r="B51" s="23">
+        <v>5</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="23">
+        <v>5</v>
+      </c>
+      <c r="J51" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M51" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="W51" s="27"/>
+    </row>
+    <row r="52" spans="2:23">
+      <c r="B52" s="23">
+        <v>6</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="23">
+        <v>6</v>
+      </c>
+      <c r="J52" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K52" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="L52" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="M52" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="N52" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="W52" s="27"/>
+    </row>
+    <row r="53" spans="2:23">
+      <c r="B53" s="23">
+        <v>7</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F53" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G53" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="23">
+        <v>7</v>
+      </c>
+      <c r="J53" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="N53" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="W53" s="27"/>
+    </row>
+    <row r="54" spans="2:23">
+      <c r="B54" s="23">
+        <v>8</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="23">
+        <v>8</v>
+      </c>
+      <c r="J54" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="K54" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L54" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M54" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="N54" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="W54" s="27"/>
+    </row>
+    <row r="55" spans="2:23">
+      <c r="B55" s="23">
+        <v>9</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" s="23">
+        <v>9</v>
+      </c>
+      <c r="J55" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="K55" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="L55" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M55" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="N55" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="W55" s="27"/>
+    </row>
+    <row r="56" spans="2:23">
+      <c r="B56" s="23">
+        <v>10</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="23">
+        <v>10</v>
+      </c>
+      <c r="J56" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K56" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="W56" s="27"/>
+    </row>
+    <row r="57" spans="2:23">
+      <c r="B57" s="23">
+        <v>11</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="23">
+        <v>11</v>
+      </c>
+      <c r="J57" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K57" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="M57" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="N57" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="W57" s="27"/>
+    </row>
+    <row r="58" spans="2:23">
+      <c r="B58" s="23">
+        <v>12</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I58" s="23">
+        <v>12</v>
+      </c>
+      <c r="J58" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K58" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L58" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M58" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="N58" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="W58" s="27"/>
+    </row>
+    <row r="59" spans="2:23">
+      <c r="B59" s="23">
+        <v>13</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D59" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="G59" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" s="23">
+        <v>13</v>
+      </c>
+      <c r="J59" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L59" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M59" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="N59" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="W59" s="27"/>
+    </row>
+    <row r="60" spans="2:23">
+      <c r="B60" s="23">
+        <v>14</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="23">
+        <v>14</v>
+      </c>
+      <c r="J60" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="K60" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="L60" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="N60" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="W60" s="27"/>
+    </row>
+    <row r="61" spans="2:23">
+      <c r="B61" s="23">
+        <v>15</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D61" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" s="23">
+        <v>15</v>
+      </c>
+      <c r="J61" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="K61" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="M61" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="W61" s="27"/>
+    </row>
+    <row r="62" spans="2:23">
+      <c r="B62" s="23">
+        <v>16</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="23">
+        <v>16</v>
+      </c>
+      <c r="J62" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="K62" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="L62" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M62" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="N62" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="W62" s="27"/>
+    </row>
+    <row r="63" spans="2:23">
+      <c r="B63" s="23">
+        <v>17</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" s="23">
+        <v>17</v>
+      </c>
+      <c r="J63" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K63" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L63" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M63" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="N63" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="W63" s="27"/>
+    </row>
+    <row r="64" spans="2:23">
+      <c r="B64" s="23">
+        <v>18</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="23">
+        <v>18</v>
+      </c>
+      <c r="J64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K64" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="L64" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M64" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="N64" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="W64" s="27"/>
+    </row>
+    <row r="65" spans="2:23">
+      <c r="B65" s="23">
+        <v>19</v>
+      </c>
+      <c r="C65" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65" s="23">
+        <v>19</v>
+      </c>
+      <c r="J65" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="L65" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="M65" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="N65" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="W65" s="27"/>
+    </row>
+    <row r="66" spans="2:14">
+      <c r="B66" s="23">
+        <v>20</v>
+      </c>
+      <c r="C66" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" s="23">
+        <v>20</v>
+      </c>
+      <c r="J66" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="K66" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L66" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M66" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="N66" s="24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14">
+      <c r="B67" s="23">
+        <v>21</v>
+      </c>
+      <c r="C67" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="G67" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I67" s="23">
+        <v>21</v>
+      </c>
+      <c r="J67" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K67" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="M67" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="N67" s="24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" ht="19" customHeight="1" spans="2:14">
+      <c r="B68" s="23">
+        <v>22</v>
+      </c>
+      <c r="C68" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68" s="23">
+        <v>22</v>
+      </c>
+      <c r="J68" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K68" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L68" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="M68" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N68" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14">
+      <c r="B69" s="23">
+        <v>23</v>
+      </c>
+      <c r="C69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I69" s="23">
+        <v>23</v>
+      </c>
+      <c r="J69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="K69" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="L69" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="M69" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N69" s="24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14">
+      <c r="B70" s="23">
+        <v>24</v>
+      </c>
+      <c r="C70" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F70" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="G70" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I70" s="23">
+        <v>24</v>
+      </c>
+      <c r="J70" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="K70" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="L70" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="N70" s="24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14">
+      <c r="B71" s="23">
+        <v>25</v>
+      </c>
+      <c r="C71" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="23">
+        <v>25</v>
+      </c>
+      <c r="J71" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="K71" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="L71" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="M71" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="N71" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14">
+      <c r="B72" s="23">
+        <v>26</v>
+      </c>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F72" s="24"/>
+      <c r="G72" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="23">
+        <v>26</v>
+      </c>
+      <c r="J72" s="24"/>
+      <c r="K72" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="L72" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="M72" s="24"/>
+      <c r="N72" s="24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14">
+      <c r="B73" s="23">
+        <v>27</v>
+      </c>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I73" s="23">
+        <v>27</v>
+      </c>
+      <c r="J73" s="24"/>
+      <c r="K73" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M73" s="24"/>
+      <c r="N73" s="24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14">
+      <c r="B74" s="23">
+        <v>28</v>
+      </c>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I74" s="23">
+        <v>28</v>
+      </c>
+      <c r="J74" s="24"/>
+      <c r="K74" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="L74" s="24"/>
+      <c r="M74" s="24"/>
+      <c r="N74" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14">
+      <c r="B75" s="23">
+        <v>29</v>
+      </c>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="23">
+        <v>29</v>
+      </c>
+      <c r="J75" s="24"/>
+      <c r="K75" s="24"/>
+      <c r="L75" s="24"/>
+      <c r="M75" s="24"/>
+      <c r="N75" s="24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14">
+      <c r="B76" s="23">
+        <v>30</v>
+      </c>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I76" s="23">
+        <v>30</v>
+      </c>
+      <c r="J76" s="24"/>
+      <c r="K76" s="24"/>
+      <c r="L76" s="24"/>
+      <c r="M76" s="24"/>
+      <c r="N76" s="24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14">
+      <c r="B77" s="23">
+        <v>31</v>
+      </c>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I77" s="23">
+        <v>31</v>
+      </c>
+      <c r="J77" s="24"/>
+      <c r="K77" s="24"/>
+      <c r="L77" s="24"/>
+      <c r="M77" s="24"/>
+      <c r="N77" s="24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14">
+      <c r="B78" s="23">
+        <v>32</v>
+      </c>
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I78" s="23">
+        <v>32</v>
+      </c>
+      <c r="J78" s="24"/>
+      <c r="K78" s="24"/>
+      <c r="L78" s="24"/>
+      <c r="M78" s="24"/>
+      <c r="N78" s="24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14">
+      <c r="B79" s="23">
+        <v>33</v>
+      </c>
+      <c r="C79" s="24"/>
+      <c r="D79" s="24"/>
+      <c r="E79" s="24"/>
+      <c r="F79" s="24"/>
+      <c r="G79" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" s="23">
+        <v>33</v>
+      </c>
+      <c r="J79" s="24"/>
+      <c r="K79" s="24"/>
+      <c r="L79" s="24"/>
+      <c r="M79" s="24"/>
+      <c r="N79" s="24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14">
+      <c r="B80" s="23">
+        <v>34</v>
+      </c>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" s="23">
+        <v>34</v>
+      </c>
+      <c r="J80" s="24"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="24"/>
+      <c r="N80" s="24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="2:25">
+      <c r="B82" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P82" s="6"/>
+      <c r="S82" s="6"/>
+      <c r="T82" s="6"/>
+      <c r="U82" s="6"/>
+      <c r="X82" s="6"/>
+      <c r="Y82" s="6"/>
+    </row>
+    <row r="83" spans="16:25">
+      <c r="P83" s="6"/>
+      <c r="S83" s="6"/>
+      <c r="T83" s="6"/>
+      <c r="U83" s="6"/>
+      <c r="X83" s="6"/>
+      <c r="Y83" s="6"/>
+    </row>
+    <row r="84" spans="2:21">
+      <c r="B84" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C84" s="29">
+        <v>25</v>
+      </c>
+      <c r="D84" s="6"/>
+      <c r="E84" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="F84" s="29">
+        <v>20</v>
+      </c>
+      <c r="H84" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="I84" s="29">
+        <v>15</v>
+      </c>
+      <c r="J84" s="6"/>
+      <c r="K84" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L84" s="29">
+        <v>10</v>
+      </c>
+      <c r="N84" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="O84" s="29">
+        <v>6</v>
+      </c>
+      <c r="P84" s="6"/>
+      <c r="U84" s="6"/>
+    </row>
+    <row r="85" spans="2:21">
+      <c r="B85" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C85" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E85" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="F85" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H85" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="I85" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="K85" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="L85" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="N85" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="O85" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="P85" s="6"/>
+      <c r="U85" s="6"/>
+    </row>
+    <row r="86" spans="2:21">
+      <c r="B86" s="29">
+        <v>2</v>
+      </c>
+      <c r="C86" s="29">
+        <v>11</v>
+      </c>
+      <c r="E86" s="29">
+        <v>3</v>
+      </c>
+      <c r="F86" s="29">
+        <v>12</v>
+      </c>
+      <c r="H86" s="29">
+        <v>5</v>
+      </c>
+      <c r="I86" s="29">
+        <v>15</v>
+      </c>
+      <c r="K86" s="29">
+        <v>10</v>
+      </c>
+      <c r="L86" s="29">
+        <v>22</v>
+      </c>
+      <c r="N86" s="29">
+        <v>15</v>
+      </c>
+      <c r="O86" s="29">
+        <v>18</v>
+      </c>
+      <c r="P86" s="6"/>
+      <c r="U86" s="6"/>
+    </row>
+    <row r="87" spans="2:21">
+      <c r="B87" s="29">
+        <v>3</v>
+      </c>
+      <c r="C87" s="29">
+        <v>14</v>
+      </c>
+      <c r="E87" s="29">
+        <v>5</v>
+      </c>
+      <c r="F87" s="29">
+        <v>14</v>
+      </c>
+      <c r="H87" s="29">
+        <v>8</v>
+      </c>
+      <c r="I87" s="29">
+        <v>13</v>
+      </c>
+      <c r="K87" s="29">
+        <v>15</v>
+      </c>
+      <c r="L87" s="29">
+        <v>12</v>
+      </c>
+      <c r="N87" s="29">
+        <v>30</v>
+      </c>
+      <c r="O87" s="29">
+        <v>10</v>
+      </c>
+      <c r="P87" s="6"/>
+      <c r="U87" s="6"/>
+    </row>
+    <row r="88" spans="2:21">
+      <c r="B88" s="29">
+        <v>5</v>
+      </c>
+      <c r="C88" s="29">
+        <v>15</v>
+      </c>
+      <c r="E88" s="29">
+        <v>8</v>
+      </c>
+      <c r="F88" s="29">
+        <v>6</v>
+      </c>
+      <c r="H88" s="29">
+        <v>10</v>
+      </c>
+      <c r="I88" s="29">
+        <v>6</v>
+      </c>
+      <c r="K88" s="29">
+        <v>30</v>
+      </c>
+      <c r="L88" s="29">
+        <v>1</v>
+      </c>
+      <c r="N88" s="29">
+        <v>40</v>
+      </c>
+      <c r="O88" s="29">
+        <v>1</v>
+      </c>
+      <c r="P88" s="6"/>
+      <c r="U88" s="6"/>
+    </row>
+    <row r="89" spans="2:21">
+      <c r="B89" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C89" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E89" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F89" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H89" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="I89" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="K89" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="L89" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="N89" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="O89" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="P89" s="6"/>
+      <c r="U89" s="6"/>
+    </row>
+    <row r="90" spans="2:21">
+      <c r="B90" s="29">
+        <v>0</v>
+      </c>
+      <c r="C90" s="29">
+        <v>8</v>
+      </c>
+      <c r="E90" s="29">
+        <v>0</v>
+      </c>
+      <c r="F90" s="29">
+        <v>8</v>
+      </c>
+      <c r="H90" s="29">
+        <v>0</v>
+      </c>
+      <c r="I90" s="29">
+        <v>8</v>
+      </c>
+      <c r="K90" s="29">
+        <v>0</v>
+      </c>
+      <c r="L90" s="29">
+        <v>14</v>
+      </c>
+      <c r="N90" s="29">
+        <v>0</v>
+      </c>
+      <c r="O90" s="29">
+        <v>9</v>
+      </c>
+      <c r="P90" s="6"/>
+      <c r="U90" s="6"/>
+    </row>
+    <row r="91" spans="2:21">
+      <c r="B91" s="29">
+        <v>1</v>
+      </c>
+      <c r="C91" s="29">
+        <v>14</v>
+      </c>
+      <c r="E91" s="29">
+        <v>1</v>
+      </c>
+      <c r="F91" s="29">
+        <v>14</v>
+      </c>
+      <c r="H91" s="29">
+        <v>1</v>
+      </c>
+      <c r="I91" s="29">
+        <v>14</v>
+      </c>
+      <c r="K91" s="29">
+        <v>1</v>
+      </c>
+      <c r="L91" s="29">
+        <v>14</v>
+      </c>
+      <c r="N91" s="29">
+        <v>1</v>
+      </c>
+      <c r="O91" s="29">
+        <v>14</v>
+      </c>
+      <c r="P91" s="6"/>
+      <c r="U91" s="6"/>
+    </row>
+    <row r="92" spans="2:21">
+      <c r="B92" s="29">
+        <v>2</v>
+      </c>
+      <c r="C92" s="29">
+        <v>12</v>
+      </c>
+      <c r="E92" s="29">
+        <v>2</v>
+      </c>
+      <c r="F92" s="29">
+        <v>12</v>
+      </c>
+      <c r="H92" s="29">
+        <v>2</v>
+      </c>
+      <c r="I92" s="29">
+        <v>13</v>
+      </c>
+      <c r="K92" s="29">
+        <v>2</v>
+      </c>
+      <c r="L92" s="29">
+        <v>8</v>
+      </c>
+      <c r="N92" s="29">
+        <v>2</v>
+      </c>
+      <c r="O92" s="29">
+        <v>14</v>
+      </c>
+      <c r="P92" s="6"/>
+      <c r="U92" s="6"/>
+    </row>
+    <row r="93" spans="2:15">
+      <c r="B93" s="29">
+        <v>3</v>
+      </c>
+      <c r="C93" s="29">
+        <v>5</v>
+      </c>
+      <c r="E93" s="29">
+        <v>3</v>
+      </c>
+      <c r="F93" s="29">
+        <v>5</v>
+      </c>
+      <c r="H93" s="29">
+        <v>3</v>
+      </c>
+      <c r="I93" s="29">
+        <v>5</v>
+      </c>
+      <c r="K93" s="29">
+        <v>3</v>
+      </c>
+      <c r="L93" s="29">
+        <v>4</v>
+      </c>
+      <c r="N93" s="29">
+        <v>3</v>
+      </c>
+      <c r="O93" s="29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C97" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="D97" s="5"/>
+      <c r="E97" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F97" s="28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="28">
+        <v>25</v>
+      </c>
+      <c r="C98" s="29">
+        <v>1</v>
+      </c>
+      <c r="E98" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F98" s="29">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6">
+      <c r="B99" s="28">
+        <v>20</v>
+      </c>
+      <c r="C99" s="29">
+        <v>3</v>
+      </c>
+      <c r="E99" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F99" s="29">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="28">
+        <v>15</v>
+      </c>
+      <c r="C100" s="29">
+        <v>5</v>
+      </c>
+      <c r="E100" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="F100" s="29">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="28">
+        <v>10</v>
+      </c>
+      <c r="C101" s="29">
+        <v>4</v>
+      </c>
+      <c r="E101" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F101" s="29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="28">
+        <v>6</v>
+      </c>
+      <c r="C102" s="29">
+        <v>1</v>
+      </c>
+      <c r="E102" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="F102" s="29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+    </row>
+    <row r="104" spans="2:3">
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="I44:N44"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="C20:C24"/>
+    <mergeCell ref="D20:D24"/>
+    <mergeCell ref="E20:E24"/>
+    <mergeCell ref="F20:F24"/>
+    <mergeCell ref="G20:G24"/>
+    <mergeCell ref="H20:H24"/>
+    <mergeCell ref="I20:I24"/>
+    <mergeCell ref="J20:J24"/>
+    <mergeCell ref="K20:K24"/>
+    <mergeCell ref="L20:L24"/>
+    <mergeCell ref="M20:M24"/>
+    <mergeCell ref="N20:N24"/>
+    <mergeCell ref="O20:O24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B2:N2"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="8.83333333333333" style="5"/>
+    <col min="2" max="4" width="15.6666666666667" style="6" customWidth="1"/>
+    <col min="5" max="6" width="8.83333333333333" style="5"/>
+    <col min="7" max="9" width="15.6666666666667" style="6" customWidth="1"/>
+    <col min="10" max="11" width="8.83333333333333" style="5"/>
+    <col min="12" max="14" width="15.6666666666667" style="6" customWidth="1"/>
+    <col min="15" max="16384" width="8.83333333333333" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="20.25" spans="2:14">
+      <c r="B2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="G2" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B2:R30"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="16384" width="11" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="18:18">
+      <c r="R30" s="30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape"/>
+  <headerFooter/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="35" max="16383" man="1"/>
+  </rowBreaks>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="22" max="1048575" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.8761904761905" customWidth="1"/>
-    <col min="4" max="5" width="14.1238095238095" customWidth="1"/>
-    <col min="6" max="6" width="9.37142857142857" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5047619047619" customWidth="1"/>
-    <col min="9" max="9" width="5.24761904761905" customWidth="1"/>
-    <col min="10" max="10" width="12.1238095238095" customWidth="1"/>
-    <col min="11" max="11" width="15.1238095238095" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="19" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.875" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5083333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" ht="99" customHeight="1" spans="1:12">
+      <c r="A3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="8:11">
+      <c r="H5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="1">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K5" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="8:11">
+      <c r="H6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J6" s="1">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K6" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="8:11">
+      <c r="H7" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J7" s="1">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="K7" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="8:10">
+      <c r="H9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="8:10">
+      <c r="H10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J10" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="8:10">
+      <c r="H11" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J11" s="1">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="8:11">
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="8:11">
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="8:11">
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="8:10">
-      <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="8:10">
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="8:10">
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
     </row>
     <row r="12" spans="8:11">
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" t="s">
-        <v>39</v>
+      <c r="H12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
